--- a/src-tauri/tests/fixtures/2026年4月分析/活动量/重庆宜新.xlsx
+++ b/src-tauri/tests/fixtures/2026年4月分析/活动量/重庆宜新.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="填写说明" sheetId="4" r:id="rId1"/>
-    <sheet name="写字楼和商业综合体类" sheetId="2" r:id="rId2"/>
+    <sheet name="商写类" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
